--- a/psp/kp_health.xlsx
+++ b/psp/kp_health.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/sql-server/psp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E032B55-1521-784F-AD54-D10D4C7E67A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B32B29CB-99AA-0743-BF86-04B8B766C06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="400" yWindow="600" windowWidth="25440" windowHeight="15800" activeTab="2" xr2:uid="{9725C3B4-3607-C246-8F87-D607CF95380C}"/>
   </bookViews>
